--- a/artfynd/A 9745-2022 artfynd.xlsx
+++ b/artfynd/A 9745-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116812927</v>
+        <v>116812474</v>
       </c>
       <c r="B2" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borås (Borås), Upl</t>
+          <t>Borås, Borås, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>678172</v>
+        <v>678394</v>
       </c>
       <c r="R2" t="n">
-        <v>6607747</v>
+        <v>6607694</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2024-05-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,31 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116813380</v>
+        <v>116812926</v>
       </c>
       <c r="B3" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,14 +811,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häggtorp (Lindholmen), Upl</t>
+          <t>Borås, Borås, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>678041</v>
+        <v>678162</v>
       </c>
       <c r="R3" t="n">
-        <v>6607823</v>
+        <v>6607754</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,19 +877,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116812926</v>
+        <v>116813380</v>
       </c>
       <c r="B4" t="n">
-        <v>57294</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -941,14 +916,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Borås (Borås), Upl</t>
+          <t>Häggtorp, Lindholmen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>678162</v>
+        <v>678041</v>
       </c>
       <c r="R4" t="n">
-        <v>6607754</v>
+        <v>6607823</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,6 +979,113 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116812927</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Borås, Borås, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>678172</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6607747</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vada</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
